--- a/KatalonData/VVTApiIVT/VVTApiIVT_CreditDebit_Card.xlsx
+++ b/KatalonData/VVTApiIVT/VVTApiIVT_CreditDebit_Card.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\t470258\Documents\VPS-Katalon\KatalonData\VVTApiIVT\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EE456F5E-FF4E-4FFA-AF0A-98D549BAEF21}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{420715BB-81E6-4BBB-A2D5-72FDE9440F84}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" activeTab="2" xr2:uid="{A171AD99-6CB3-481A-968B-971B4AF2105E}"/>
   </bookViews>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="49" uniqueCount="35">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="76" uniqueCount="55">
   <si>
     <t>Result</t>
   </si>
@@ -132,9 +132,6 @@
     <t>Country</t>
   </si>
   <si>
-    <t>Expiry</t>
-  </si>
-  <si>
     <t>Address</t>
   </si>
   <si>
@@ -181,13 +178,76 @@
   </si>
   <si>
     <t>Mandatory + Non</t>
+  </si>
+  <si>
+    <t>ExpMM</t>
+  </si>
+  <si>
+    <t>ExpYYYY</t>
+  </si>
+  <si>
+    <t>4761730000000011</t>
+  </si>
+  <si>
+    <t>bbg@email.com</t>
+  </si>
+  <si>
+    <t>444-555-6666</t>
+  </si>
+  <si>
+    <t>1853 Mandan Terace</t>
+  </si>
+  <si>
+    <t>20770</t>
+  </si>
+  <si>
+    <t>BBG1</t>
+  </si>
+  <si>
+    <t>6510000000000216</t>
+  </si>
+  <si>
+    <t>09</t>
+  </si>
+  <si>
+    <t>BBG2</t>
+  </si>
+  <si>
+    <t>BBG3</t>
+  </si>
+  <si>
+    <t>BBG4</t>
+  </si>
+  <si>
+    <t>BBG5</t>
+  </si>
+  <si>
+    <t>BBG6</t>
+  </si>
+  <si>
+    <t>BBG7</t>
+  </si>
+  <si>
+    <t>BBG8</t>
+  </si>
+  <si>
+    <t>BBG9</t>
+  </si>
+  <si>
+    <t>BBG10</t>
+  </si>
+  <si>
+    <t>22201</t>
+  </si>
+  <si>
+    <t>1234 Mandan Terace</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="6" x14ac:knownFonts="1">
+  <fonts count="7" x14ac:knownFonts="1">
     <font>
       <sz val="10"/>
       <color theme="1"/>
@@ -225,13 +285,38 @@
       <name val="Century Gothic"/>
       <family val="2"/>
     </font>
+    <font>
+      <u/>
+      <sz val="10"/>
+      <color theme="10"/>
+      <name val="Century Gothic"/>
+      <family val="2"/>
+    </font>
   </fonts>
-  <fills count="2">
+  <fills count="5">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFF00"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.59999389629810485"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.59999389629810485"/>
+        <bgColor indexed="64"/>
+      </patternFill>
     </fill>
   </fills>
   <borders count="2">
@@ -258,10 +343,11 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="15">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="49" fontId="3" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
@@ -284,11 +370,30 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
-    <xf numFmtId="49" fontId="3" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="3" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="3" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="3" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
   </cellXfs>
-  <cellStyles count="1">
+  <cellStyles count="2">
+    <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
@@ -733,6 +838,9 @@
       <c r="E2">
         <v>10</v>
       </c>
+      <c r="F2">
+        <v>30</v>
+      </c>
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.25">
       <c r="D3" t="s">
@@ -741,6 +849,9 @@
       <c r="E3">
         <v>5</v>
       </c>
+      <c r="F3">
+        <v>30</v>
+      </c>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.25">
       <c r="D4" t="s">
@@ -748,6 +859,9 @@
       </c>
       <c r="E4">
         <v>20</v>
+      </c>
+      <c r="F4">
+        <v>30</v>
       </c>
     </row>
   </sheetData>
@@ -757,18 +871,30 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BF6F2E4C-CFE1-482F-B245-5C18A941E254}">
-  <dimension ref="A1:Z3"/>
+  <dimension ref="A1:AA4"/>
   <sheetFormatPr defaultRowHeight="12.5" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="8.08984375" customWidth="1"/>
-    <col min="2" max="2" width="14.26953125" customWidth="1"/>
-    <col min="3" max="3" width="17.08984375" customWidth="1"/>
-    <col min="5" max="5" width="16.90625" customWidth="1"/>
-    <col min="6" max="6" width="8.7265625" customWidth="1"/>
-    <col min="7" max="7" width="7.81640625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="8.08984375" style="4" customWidth="1"/>
+    <col min="2" max="2" width="14.26953125" style="4" customWidth="1"/>
+    <col min="3" max="3" width="26.1796875" style="4" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="8.7265625" style="4"/>
+    <col min="5" max="5" width="18.36328125" style="9" customWidth="1"/>
+    <col min="6" max="6" width="7.36328125" style="4" customWidth="1"/>
+    <col min="7" max="7" width="8.7265625" style="4" customWidth="1"/>
+    <col min="8" max="8" width="7.81640625" style="4" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="6.54296875" style="4" customWidth="1"/>
+    <col min="10" max="10" width="15.6328125" style="4" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="12.08984375" style="4" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="5.7265625" style="4" customWidth="1"/>
+    <col min="13" max="13" width="8.453125" style="4" customWidth="1"/>
+    <col min="14" max="14" width="20.26953125" style="4" customWidth="1"/>
+    <col min="15" max="15" width="8.7265625" style="4"/>
+    <col min="16" max="16" width="6.1796875" style="4" customWidth="1"/>
+    <col min="17" max="17" width="5.08984375" style="4" customWidth="1"/>
+    <col min="18" max="16384" width="8.7265625" style="4"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:26" ht="25" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:27" ht="25" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -781,91 +907,206 @@
       <c r="D1" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="8" t="s">
+      <c r="E1" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="F1" s="8" t="s">
+      <c r="F1" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="I1" s="12" t="s">
+        <v>14</v>
+      </c>
+      <c r="J1" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="K1" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="L1" s="13" t="s">
+        <v>1</v>
+      </c>
+      <c r="M1" s="13" t="s">
+        <v>17</v>
+      </c>
+      <c r="N1" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="G1" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="H1" s="8" t="s">
-        <v>14</v>
-      </c>
-      <c r="I1" s="8" t="s">
-        <v>15</v>
-      </c>
-      <c r="J1" s="8" t="s">
-        <v>16</v>
-      </c>
-      <c r="K1" s="8" t="s">
-        <v>1</v>
-      </c>
-      <c r="L1" s="8" t="s">
-        <v>17</v>
-      </c>
-      <c r="M1" s="8" t="s">
+      <c r="O1" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="N1" s="8" t="s">
+      <c r="P1" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="O1" s="8" t="s">
+      <c r="Q1" s="13" t="s">
         <v>21</v>
       </c>
-      <c r="P1" s="8" t="s">
+      <c r="R1" s="8" t="s">
         <v>22</v>
       </c>
-      <c r="Q1" s="8" t="s">
+      <c r="S1" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="R1" s="8" t="s">
+      <c r="T1" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="S1" s="8" t="s">
+      <c r="U1" s="1" t="s">
         <v>25</v>
       </c>
-      <c r="T1" s="8" t="s">
+      <c r="V1" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="U1" s="8" t="s">
+      <c r="W1" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="V1" s="8" t="s">
+      <c r="X1" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="W1" s="8" t="s">
+      <c r="Y1" s="1" t="s">
         <v>29</v>
       </c>
-      <c r="X1" s="8" t="s">
+      <c r="Z1" s="1" t="s">
         <v>30</v>
       </c>
-      <c r="Y1" s="8" t="s">
+      <c r="AA1" s="1" t="s">
         <v>31</v>
       </c>
-      <c r="Z1" s="8" t="s">
+    </row>
+    <row r="2" spans="1:27" x14ac:dyDescent="0.25">
+      <c r="C2" s="4" t="s">
         <v>32</v>
       </c>
-    </row>
-    <row r="2" spans="1:26" x14ac:dyDescent="0.25">
-      <c r="C2" t="s">
+      <c r="D2" s="4" t="s">
+        <v>4</v>
+      </c>
+      <c r="E2" s="9" t="s">
+        <v>36</v>
+      </c>
+      <c r="F2" s="4">
+        <v>12</v>
+      </c>
+      <c r="G2" s="4">
+        <v>2028</v>
+      </c>
+      <c r="H2" s="4">
+        <v>201</v>
+      </c>
+      <c r="J2" s="10" t="s">
+        <v>37</v>
+      </c>
+      <c r="N2" s="11" t="s">
+        <v>39</v>
+      </c>
+      <c r="O2" s="11" t="s">
+        <v>53</v>
+      </c>
+      <c r="R2" s="4" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="3" spans="1:27" x14ac:dyDescent="0.25">
+      <c r="C3" s="4" t="s">
         <v>33</v>
       </c>
-      <c r="D2" t="s">
+      <c r="D3" s="4" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="3" spans="1:26" x14ac:dyDescent="0.25">
-      <c r="C3" t="s">
-        <v>34</v>
-      </c>
-      <c r="D3" t="s">
+      <c r="E3" s="9" t="s">
+        <v>42</v>
+      </c>
+      <c r="F3" s="11" t="s">
+        <v>43</v>
+      </c>
+      <c r="G3" s="4">
+        <v>2028</v>
+      </c>
+      <c r="H3" s="4">
+        <v>201</v>
+      </c>
+      <c r="J3" s="10" t="s">
+        <v>37</v>
+      </c>
+      <c r="K3" s="4" t="s">
+        <v>38</v>
+      </c>
+      <c r="N3" s="11" t="s">
+        <v>54</v>
+      </c>
+      <c r="O3" s="11" t="s">
+        <v>40</v>
+      </c>
+      <c r="R3" s="4" t="s">
+        <v>41</v>
+      </c>
+      <c r="S3" s="4" t="s">
+        <v>44</v>
+      </c>
+      <c r="T3" s="4" t="s">
+        <v>45</v>
+      </c>
+      <c r="U3" s="4" t="s">
+        <v>46</v>
+      </c>
+      <c r="V3" s="4" t="s">
+        <v>47</v>
+      </c>
+      <c r="W3" s="4" t="s">
+        <v>48</v>
+      </c>
+      <c r="X3" s="4" t="s">
+        <v>49</v>
+      </c>
+      <c r="Y3" s="4" t="s">
+        <v>50</v>
+      </c>
+      <c r="Z3" s="4" t="s">
+        <v>51</v>
+      </c>
+      <c r="AA3" s="4" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="4" spans="1:27" x14ac:dyDescent="0.25">
+      <c r="D4" s="4" t="s">
         <v>4</v>
+      </c>
+      <c r="E4" s="9" t="s">
+        <v>36</v>
+      </c>
+      <c r="F4" s="4">
+        <v>12</v>
+      </c>
+      <c r="G4" s="4">
+        <v>2028</v>
+      </c>
+      <c r="H4" s="4">
+        <v>201</v>
+      </c>
+      <c r="J4" s="10" t="s">
+        <v>37</v>
+      </c>
+      <c r="N4" s="11" t="s">
+        <v>39</v>
+      </c>
+      <c r="O4" s="14">
+        <v>12345</v>
+      </c>
+      <c r="R4" s="4" t="s">
+        <v>41</v>
       </c>
     </row>
   </sheetData>
   <phoneticPr fontId="2" type="noConversion"/>
+  <hyperlinks>
+    <hyperlink ref="J2" r:id="rId1" xr:uid="{82457AE3-4FA9-432B-B055-CC9AFF3BA944}"/>
+    <hyperlink ref="J3" r:id="rId2" xr:uid="{B014B5E2-08A4-4E68-9CFF-E858F4E26AB6}"/>
+    <hyperlink ref="J4" r:id="rId3" xr:uid="{1A4AE20D-96A2-4DCF-B367-2D01EED615DE}"/>
+  </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>